--- a/rcads/data/xls/90_Languages.xlsx
+++ b/rcads/data/xls/90_Languages.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_90_Languages"/>
   </sheets>
   <definedNames>
-    <definedName name="_90_Languages">'_90_Languages'!$A$1:$H$42</definedName>
+    <definedName name="_90_Languages">'_90_Languages'!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -374,15 +374,10 @@
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
-          <t>ISO 3166 Country Code</t>
+          <t>LanguageinLanguage</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>LanguageinLanguage</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>LanguageinLanguage (Latin letters)</t>
         </is>
@@ -407,12 +402,7 @@
           <t>ENG</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>English</t>
         </is>
@@ -437,12 +427,12 @@
           <t>ARA</t>
         </is>
       </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>	اَلْعَرَبِيَّةُ</t>
+        </is>
+      </c>
       <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>	اَلْعَرَبِيَّةُ</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>al-ʿarabiyyah</t>
         </is>
@@ -492,12 +482,7 @@
           <t>DAN</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>Dansk</t>
         </is>
@@ -522,12 +507,7 @@
           <t>DUT</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
@@ -552,7 +532,7 @@
           <t>EST</t>
         </is>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>Eesti keel</t>
         </is>
@@ -577,7 +557,7 @@
           <t>FIN</t>
         </is>
       </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>Suomi</t>
         </is>
@@ -602,12 +582,7 @@
           <t>FRE</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>Français</t>
         </is>
@@ -632,12 +607,7 @@
           <t>GER</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>Deutsch</t>
         </is>
@@ -662,12 +632,12 @@
           <t>GRE</t>
         </is>
       </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Νέα Ελληνικά</t>
+        </is>
+      </c>
       <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>Νέα Ελληνικά</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Néa Ellêniká</t>
         </is>
@@ -692,7 +662,7 @@
           <t>HUN</t>
         </is>
       </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>Magyar nyelv</t>
         </is>
@@ -717,7 +687,7 @@
           <t>ICE</t>
         </is>
       </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>Íslenska</t>
         </is>
@@ -744,15 +714,10 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>日本語</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Nihongo</t>
         </is>
@@ -797,7 +762,7 @@
           <t>LIT</t>
         </is>
       </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>Lietuvių</t>
         </is>
@@ -822,7 +787,7 @@
           <t>NOR</t>
         </is>
       </c>
-      <c r="H17" s="0" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>Norsk</t>
         </is>
@@ -847,12 +812,12 @@
           <t>PER</t>
         </is>
       </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>فارسی</t>
+        </is>
+      </c>
       <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>فارسی</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>Fārsiy</t>
         </is>
@@ -877,7 +842,7 @@
           <t>POL</t>
         </is>
       </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>Polski</t>
         </is>
@@ -902,12 +867,7 @@
           <t>POR</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
@@ -932,7 +892,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="H21" s="0" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>Slovenščina</t>
         </is>
@@ -957,7 +917,7 @@
           <t>SPA</t>
         </is>
       </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>Español</t>
         </is>
@@ -982,7 +942,7 @@
           <t>SWE</t>
         </is>
       </c>
-      <c r="H23" s="0" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>Svenska</t>
         </is>
@@ -1007,7 +967,7 @@
           <t>TUR</t>
         </is>
       </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>Türkçe</t>
         </is>
@@ -1032,12 +992,12 @@
           <t>URD</t>
         </is>
       </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>اُردُو</t>
+        </is>
+      </c>
       <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>اُردُو</t>
-        </is>
-      </c>
-      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>Urduw</t>
         </is>
@@ -1087,12 +1047,12 @@
           <t>SWA</t>
         </is>
       </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>كِسوَحِيلِ</t>
+        </is>
+      </c>
       <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>كِسوَحِيلِ</t>
-        </is>
-      </c>
-      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>Kiswahili</t>
         </is>
@@ -1117,12 +1077,12 @@
           <t>SRP</t>
         </is>
       </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>Српски</t>
+        </is>
+      </c>
       <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>Српски</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>Srpski</t>
         </is>
@@ -1147,12 +1107,12 @@
           <t>MSA</t>
         </is>
       </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>بهاس ملايو</t>
+        </is>
+      </c>
       <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>بهاس ملايو</t>
-        </is>
-      </c>
-      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>bahasa Melayu</t>
         </is>
@@ -1182,27 +1142,7 @@
       <c r="A31" s="0">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>FRE</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H31" s="0" t="inlineStr">
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>Français</t>
         </is>
@@ -1227,12 +1167,12 @@
           <t>HIN</t>
         </is>
       </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>हिन्दी</t>
+        </is>
+      </c>
       <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>हिन्दी</t>
-        </is>
-      </c>
-      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>Hindī</t>
         </is>
@@ -1257,12 +1197,12 @@
           <t>PAN</t>
         </is>
       </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>ਪੰਜਾਬੀ</t>
+        </is>
+      </c>
       <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>ਪੰਜਾਬੀ</t>
-        </is>
-      </c>
-      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>Pãjābī</t>
         </is>
@@ -1287,12 +1227,12 @@
           <t>RUS</t>
         </is>
       </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
       <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>Русский язык</t>
-        </is>
-      </c>
-      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>Russkiĭ âzyk</t>
         </is>
@@ -1317,7 +1257,7 @@
           <t>NYA</t>
         </is>
       </c>
-      <c r="H35" s="0" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>Chichewa</t>
         </is>
@@ -1342,12 +1282,12 @@
           <t>HEB</t>
         </is>
       </c>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>עברית</t>
+        </is>
+      </c>
       <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>Ivrit</t>
         </is>
@@ -1372,7 +1312,7 @@
           <t>ITA</t>
         </is>
       </c>
-      <c r="H37" s="0" t="inlineStr">
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>Italiano</t>
         </is>
@@ -1397,12 +1337,12 @@
           <t>THA</t>
         </is>
       </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>ภาษาไทย</t>
+        </is>
+      </c>
       <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>ภาษาไทย</t>
-        </is>
-      </c>
-      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>Phasa Thai</t>
         </is>
@@ -1427,7 +1367,7 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="H39" s="0" t="inlineStr">
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>Mongol xel</t>
         </is>
@@ -1452,12 +1392,12 @@
           <t>VIE</t>
         </is>
       </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t>Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>Tiếng Việt</t>
         </is>
@@ -1482,12 +1422,12 @@
           <t>MAR</t>
         </is>
       </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>मराठी</t>
+        </is>
+      </c>
       <c r="G41" s="0" t="inlineStr">
-        <is>
-          <t>मराठी</t>
-        </is>
-      </c>
-      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>Marāṭhī</t>
         </is>
@@ -1512,10 +1452,40 @@
           <t>ZUL</t>
         </is>
       </c>
-      <c r="H42" s="0" t="inlineStr">
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>isiZulu</t>
         </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="43">
+      <c r="A43" s="0">
+        <v>42</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>Albanian</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>SQI</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>Shqip</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="44">
+      <c r="A44" s="0">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
